--- a/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman. Il dit : maman, la lumière. Maman vient. Maman allume la lampe. La pièce devient claire. Papa entre. Papa dit : on appelle papa ou maman pour la lumière. On va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
+          <t>Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman. Maman, la lumière. Maman vient. Maman allume la lampe. La pièce devient claire. Papa entre. On appelle papa ou maman pour la lumière. On va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman.
+narrateur|Maman, la lumière. Maman vient. Maman allume la lampe.
+narrateur|La pièce devient claire. Papa entre.
+papa|On appelle papa ou maman pour la lumière. On va appeler un adulte.
+narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc veut la lumière. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc pose un wagon sur le chemin. La lampe reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Loïc veut la lumière. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Loïc a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1855,7 @@
           <t>narrateur|Loïc pose un wagon sur le chemin. La lampe reste allumée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loïc appelle pour la lampe</t>
+          <t>Le wagon rouge et la lampe</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rail de bois fait clic. Le ciel à la fenêtre est orange. Aniss veut la lampe. Il va appeler un adulte. Les mains avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman. Maman, la lumière. Maman vient. Maman allume la lampe. La pièce devient claire. Papa entre. On appelle papa ou maman pour la lumière. On va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
+          <t>Un rail de bois fait un petit clic. Le clic est sec, tout net. Un wagon rouge attend sur le tapis. La fenêtre est orange, tout bas. Le jour s'en va, tout doux. Le linge sent le savon, près de la porte. Maman plie une petite chemise. Aniss vit ici, avec papa et maman. Maman, le rail fait clic ! Oui. C'est le bois. Tu vois le wagon rouge ? Oui. Il attend. En ce moment, Aniss pose un rail. Puis un autre. Le chemin est encore court. La pièce devient un peu sombre. Maman, la lumière. Aniss regarde ses mains. Les mains avec les jouets. Aniss appelle maman. On va appeler un adulte. J'arrive, Aniss. Maman vient. Maman allume la lampe. La pièce devient claire. Le wagon rouge brille. Tu as appelé un adulte ? Oui, papa. Bravo, Aniss. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Aniss reprend le wagon rouge. Il le pose sur le rail. Le wagon glisse. Il fait un petit bruit de bois. Il avance ! Oui. Tu as fait du bon travail. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu fais un plus long chemin ? Oui. Papa s'assoit près du tapis. Il tend un rail. Tes mains sont avec les jouets ? Oui, maman. Bravo. La fenêtre n'est plus orange. Elle est plus sombre, dehors. La lampe fait un rond chaud. J'ai appelé un adulte. Oui. C'est bien. Aniss est calme. Le train a un petit chemin. Le linge reste près de la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman.
-narrateur|Maman, la lumière. Maman vient. Maman allume la lampe.
-narrateur|La pièce devient claire. Papa entre.
-papa|On appelle papa ou maman pour la lumière. On va appeler un adulte.
-narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.</t>
+          <t>narrateur|Un rail de bois fait un petit clic.
+narrateur|Le clic est sec, tout net.
+narrateur|Un wagon rouge attend sur le tapis.
+narrateur|La fenêtre est orange, tout bas.
+narrateur|Le jour s'en va, tout doux.
+narrateur|Le linge sent le savon, près de la porte.
+narrateur|Maman plie une petite chemise.
+narrateur|Aniss vit ici, avec papa et maman.
+enfant-m|Maman, le rail fait clic !
+maman|Oui.
+maman|C'est le bois.
+maman|Tu vois le wagon rouge ?
+enfant-m|Oui.
+enfant-m|Il attend.
+narrateur|En ce moment, Aniss pose un rail.
+narrateur|Puis un autre.
+narrateur|Le chemin est encore court.
+narrateur|La pièce devient un peu sombre.
+enfant-m|Maman, la lumière.
+narrateur|Aniss regarde ses mains.
+narrateur|Les mains avec les jouets.
+narrateur|Aniss appelle maman.
+narrateur|On va appeler un adulte.
+maman|J'arrive, Aniss.
+narrateur|Maman vient.
+narrateur|Maman allume la lampe.
+narrateur|La pièce devient claire.
+narrateur|Le wagon rouge brille.
+papa|Tu as appelé un adulte ?
+enfant-m|Oui, papa.
+papa|Bravo, Aniss.
+papa|On appelle papa ou maman pour la lumière.
+maman|Les prises sont pour les adultes.
+maman|Les mains avec les jouets.
+narrateur|Aniss reprend le wagon rouge.
+narrateur|Il le pose sur le rail.
+narrateur|Le wagon glisse.
+narrateur|Il fait un petit bruit de bois.
+enfant-m|Il avance !
+maman|Oui.
+maman|Tu as fait du bon travail.
+narrateur|Parce qu'il a appelé, la lumière est là.
+narrateur|Les mains tiennent les jouets.
+papa|Tu fais un plus long chemin ?
+enfant-m|Oui.
+narrateur|Papa s'assoit près du tapis.
+narrateur|Il tend un rail.
+maman|Tes mains sont avec les jouets ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|La fenêtre n'est plus orange.
+narrateur|Elle est plus sombre, dehors.
+narrateur|La lampe fait un rond chaud.
+enfant-m|J'ai appelé un adulte.
+papa|Oui.
+papa|C'est bien.
+narrateur|Aniss est calme.
+narrateur|Le train a un petit chemin.
+narrateur|Le linge reste près de la porte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>train_bois</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Loïc veut la lumière. Que fait-il ?</t>
+          <t>Aniss veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Loïc veut la lumière. Que fait-il ?</t>
+          <t>narrateur|Aniss veut la lumière.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Loïc a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>Aniss a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Maman. Bravo, Aniss. Tu as fait du bon travail. Les prises sont pour les adultes. Le wagon rouge reste sur le rail. La lampe reste allumée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1751,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Loïc a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>narrateur|Aniss a appelé un adulte.
+narrateur|Les mains avec les jouets.
+maman|Tu as appelé un adulte ?
+enfant-m|Oui.
+enfant-m|Maman.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+maman|Les prises sont pour les adultes.
+narrateur|Le wagon rouge reste sur le rail.
+narrateur|La lampe reste allumée.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Loïc pose un wagon sur le chemin. La lampe reste allumée.</t>
+          <t>Aniss pose un dernier wagon. Le chemin est fini. Tu ranges un rail, maintenant ? Un peu. Il pose un rail dans la boîte. Tu as fini de ranger ce rail ? Oui. Bravo. La lampe reste allumée. La chemise est pliée. Ça sent encore le savon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1928,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Loïc pose un wagon sur le chemin. La lampe reste allumée.</t>
+          <t>narrateur|Aniss pose un dernier wagon.
+narrateur|Le chemin est fini.
+maman|Tu ranges un rail, maintenant ?
+enfant-m|Un peu.
+narrateur|Il pose un rail dans la boîte.
+maman|Tu as fini de ranger ce rail ?
+enfant-m|Oui.
+maman|Bravo.
+papa|La lampe reste allumée.
+narrateur|La chemise est pliée.
+narrateur|Ça sent encore le savon.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. Le wagon rouge se repose sur le tapis. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2106,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai appelé un adulte.
+enfant-m|Les mains avec les jouets.
+maman|Bravo.
+papa|C'est du bon travail.
+narrateur|Le wagon rouge se repose sur le tapis.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rail de bois fait un petit clic. Le clic est sec, tout net. Un wagon rouge attend sur le tapis. La fenêtre est orange, tout bas. Le jour s'en va, tout doux. Le linge sent le savon, près de la porte. Maman plie une petite chemise. Aniss vit ici, avec papa et maman. Maman, le rail fait clic ! Oui. C'est le bois. Tu vois le wagon rouge ? Oui. Il attend. En ce moment, Aniss pose un rail. Puis un autre. Le chemin est encore court. La pièce devient un peu sombre. Maman, la lumière. Aniss regarde ses mains. Les mains avec les jouets. Aniss appelle maman. On va appeler un adulte. J'arrive, Aniss. Maman vient. Maman allume la lampe. La pièce devient claire. Le wagon rouge brille. Tu as appelé un adulte ? Oui, papa. Bravo, Aniss. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Aniss reprend le wagon rouge. Il le pose sur le rail. Le wagon glisse. Il fait un petit bruit de bois. Il avance ! Oui. Tu as fait du bon travail. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu fais un plus long chemin ? Oui. Papa s'assoit près du tapis. Il tend un rail. Tes mains sont avec les jouets ? Oui, maman. Bravo. La fenêtre n'est plus orange. Elle est plus sombre, dehors. La lampe fait un rond chaud. J'ai appelé un adulte. Oui. C'est bien. Aniss est calme. Le train a un petit chemin. Le linge reste près de la porte.</t>
+          <t>Un rail de bois fait un petit clic. Le clic est sec, tout net. Un wagon rouge attend sur le tapis. La fenêtre est orange, tout bas. Le jour s'en va, tout doux. Le linge sent le savon, près de la porte. Maman plie une petite chemise. Aniss vit ici, avec papa et maman. Maman, le rail fait clic ! Oui. C'est le bois. Tu vois le wagon rouge ? Oui. Il attend. En ce moment, Aniss pose un rail. Puis un autre. Le chemin est encore court. La pièce devient un peu sombre. Maman, la lumière. Aniss regarde ses mains. Les mains avec les jouets. Aniss appelle maman. On va appeler un adulte. J'arrive, Aniss. Maman vient. Maman allume la lampe. La pièce devient claire. Le wagon rouge brille. Tu as appelé un adulte ? Oui, papa. Bravo, Aniss. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Aniss reprend le wagon rouge. Il le pose sur le rail. Le wagon glisse. Il fait un petit bruit de bois. Il avance ! Oui. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu fais un plus long chemin ? Oui. Papa s'assoit près du tapis. Il tend un rail. Tes mains sont avec les jouets ? Oui, maman. Bravo. La fenêtre n'est plus orange. Elle est plus sombre, dehors. La lampe fait un rond chaud. J'ai appelé un adulte. Oui. C'est bien. Aniss est calme. Le train a un petit chemin. Le linge reste près de la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïc joue dans sa chambre. Son train en bois est par terre. Maman plie le linge près de la porte. Loïc veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Loïc appelle maman. Il dit : maman, la lumière. Maman vient. Maman allume la lampe. La pièce devient claire. Papa entre. Papa dit : on appelle papa ou maman pour la lumière. On va &lt;emphasis level="moderate"&gt;appeler&lt;/emphasis&gt; un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Loïc reprend un wagon rouge. Il fait un petit chemin. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Parce que les mains restent avec les jouets, Loïc peut jouer. Loïc est content.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rail de bois fait un petit clic. Le clic est sec, tout net. Un wagon rouge attend sur le tapis. La fenêtre est orange, tout bas. Le jour s'en va, tout doux. Le linge sent le savon, près de la porte. Maman plie une petite chemise. Aniss vit ici, avec papa et maman. Maman, le rail fait clic ! Oui. C'est le bois. Tu vois le wagon rouge ? Oui. Il attend. En ce moment, Aniss pose un rail. Puis un autre. Le chemin est encore court. La pièce devient un peu sombre. Maman, la lumière. Aniss regarde ses mains. Les mains avec les jouets. Aniss appelle maman. On va appeler un adulte. J'arrive, Aniss. Maman vient. Maman allume la lampe. La pièce devient claire. Le wagon rouge brille. Tu as appelé un adulte ? Oui, papa. Bravo, Aniss. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Aniss reprend le wagon rouge. Il le pose sur le rail. Le wagon glisse. Il fait un petit bruit de bois. Il avance ! Oui. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu fais un plus long chemin ? Oui. Papa s'assoit près du tapis. Il tend un rail. Tes mains sont avec les jouets ? Oui, maman. Bravo. La fenêtre n'est plus orange. Elle est plus sombre, dehors. La lampe fait un rond chaud. J'ai appelé un adulte. Oui. C'est bien. Aniss est calme. Le train a un petit chemin. Le linge reste près de la porte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 narrateur|Il fait un petit bruit de bois.
 enfant-m|Il avance !
 maman|Oui.
-maman|Tu as fait du bon travail.
 narrateur|Parce qu'il a appelé, la lumière est là.
 narrateur|Les mains tiennent les jouets.
 papa|Tu fais un plus long chemin ?
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Loïc veut la lumière. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1577,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Maman. Bravo, Aniss. Tu as fait du bon travail. Les prises sont pour les adultes. Le wagon rouge reste sur le rail. La lampe reste allumée.</t>
+          <t>Aniss a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Maman. Bravo, Aniss. Les prises sont pour les adultes. Le wagon rouge reste sur le rail. La lampe reste allumée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Loïc a appelé un adulte. Les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; étaient avec les jouets. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Maman. Bravo, Aniss. Les prises sont pour les adultes. Le wagon rouge reste sur le rail. La lampe reste allumée.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1757,13 +1755,11 @@
 enfant-m|Oui.
 enfant-m|Maman.
 papa|Bravo, Aniss.
-papa|Tu as fait du bon travail.
 maman|Les prises sont pour les adultes.
 narrateur|Le wagon rouge reste sur le rail.
 narrateur|La lampe reste allumée.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Loïc pose un wagon sur le chemin. La lampe reste allumée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose un dernier wagon. Le chemin est fini. Tu ranges un rail, maintenant ? Un peu. Il pose un rail dans la boîte. Tu as fini de ranger ce rail ? Oui. Bravo. La lampe reste allumée. La chemise est pliée. Ça sent encore le savon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1937,6 @@
 narrateur|Ça sent encore le savon.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. Le wagon rouge se repose sur le tapis. L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. Le wagon rouge se repose sur le tapis.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. Le wagon rouge se repose sur le tapis.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2104,9 @@
           <t>enfant-m|J'ai appelé un adulte.
 enfant-m|Les mains avec les jouets.
 maman|Bravo.
-papa|C'est du bon travail.
-narrateur|Le wagon rouge se repose sur le tapis.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le wagon rouge se repose sur le tapis.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2170,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, train en bois, fenêtre orange, linge</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loïc, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
